--- a/template_file/MasterExportTemplate.xlsx
+++ b/template_file/MasterExportTemplate.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E104F627-CAE9-4EDD-87B9-51954114CBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC58E7DA-4E53-46EF-A228-540CB93C29AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4905" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -238,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -263,8 +263,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -287,22 +285,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:colOff>590550</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>631825</xdr:colOff>
+      <xdr:colOff>895349</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>498475</xdr:rowOff>
+      <xdr:rowOff>420809</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{974578DA-4340-4469-A191-BD2281F6F514}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -311,15 +309,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="590550" y="95250"/>
+          <a:ext cx="304799" cy="325559"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -332,9 +330,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -372,7 +370,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -478,7 +476,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -620,7 +618,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -731,19 +729,19 @@
       <c r="A5" s="9"/>
       <c r="B5" s="10"/>
       <c r="C5" s="10"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
